--- a/docs/reference/TrimmedSpellListV2.xlsx
+++ b/docs/reference/TrimmedSpellListV2.xlsx
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
